--- a/erp-server/erp-server-wms/src/main/resources/excel/VwAllocationcancelTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VwAllocationcancelTemplate.xlsx
@@ -27,18 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>单据编号</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -52,6 +49,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -65,6 +68,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -78,6 +87,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -88,15 +103,6 @@
       </rPr>
       <t>取消分配数量</t>
     </r>
-  </si>
-  <si>
-    <t>{.code}</t>
-  </si>
-  <si>
-    <t>{.statusName}</t>
-  </si>
-  <si>
-    <t>{.typeName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -138,11 +144,6 @@
     </font>
     <font>
       <sz val="13"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="13"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -290,6 +291,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -633,137 +639,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -776,19 +782,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1316,62 +1313,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="16.875" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="25.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="20.875" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="1" max="1" width="16.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:4">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VwAllocationcancelTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VwAllocationcancelTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <r>
       <rPr>
@@ -103,18 +103,6 @@
       </rPr>
       <t>取消分配数量</t>
     </r>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.warehouseName}</t>
-  </si>
-  <si>
-    <t>{.fromVirtualWarehouseName}</t>
-  </si>
-  <si>
-    <t>{.qty}</t>
   </si>
 </sst>
 </file>
@@ -1337,18 +1325,10 @@
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:4">
-      <c r="A2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VwAllocationcancelTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VwAllocationcancelTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27045" windowHeight="11850"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
       <rPr>
@@ -104,6 +104,9 @@
       <t>取消分配数量</t>
     </r>
   </si>
+  <si>
+    <t>备注</t>
+  </si>
 </sst>
 </file>
 
@@ -137,6 +140,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="13"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -279,11 +287,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -627,137 +630,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -771,6 +774,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1301,16 +1307,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="17" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.875" style="3" customWidth="1"/>
     <col min="4" max="4" width="20" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1323,12 +1330,16 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:4">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+    <row r="2" s="2" customFormat="1" spans="1:5">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
